--- a/artfynd/A 5041-2025 artfynd.xlsx
+++ b/artfynd/A 5041-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122894703</v>
       </c>
       <c r="B2" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 5041-2025 artfynd.xlsx
+++ b/artfynd/A 5041-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122894703</v>
       </c>
       <c r="B2" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 5041-2025 artfynd.xlsx
+++ b/artfynd/A 5041-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122894703</v>
       </c>
       <c r="B2" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 5041-2025 artfynd.xlsx
+++ b/artfynd/A 5041-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122894703</v>
       </c>
       <c r="B2" t="n">
-        <v>78772</v>
+        <v>78775</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 5041-2025 artfynd.xlsx
+++ b/artfynd/A 5041-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>126760160</v>
       </c>
       <c r="B3" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>126760187</v>
       </c>
       <c r="B4" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>126760309</v>
       </c>
       <c r="B5" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>126759638</v>
       </c>
       <c r="B6" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 5041-2025 artfynd.xlsx
+++ b/artfynd/A 5041-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>126760160</v>
       </c>
       <c r="B3" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>126760187</v>
       </c>
       <c r="B4" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>126760309</v>
       </c>
       <c r="B5" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>126759638</v>
       </c>
       <c r="B6" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 5041-2025 artfynd.xlsx
+++ b/artfynd/A 5041-2025 artfynd.xlsx
@@ -887,7 +887,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Cecilia Persson, Tomas Fasth</t>
+          <t>Tomas Fasth, Cecilia Persson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -994,7 +994,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Cecilia Persson, Tomas Fasth</t>
+          <t>Tomas Fasth, Cecilia Persson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 5041-2025 artfynd.xlsx
+++ b/artfynd/A 5041-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>126760160</v>
       </c>
       <c r="B3" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Tomas Fasth, Cecilia Persson</t>
+          <t>Cecilia Persson, Tomas Fasth</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -897,7 +897,7 @@
         <v>126760187</v>
       </c>
       <c r="B4" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Tomas Fasth, Cecilia Persson</t>
+          <t>Cecilia Persson, Tomas Fasth</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1004,7 +1004,7 @@
         <v>126760309</v>
       </c>
       <c r="B5" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>126759638</v>
       </c>
       <c r="B6" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 5041-2025 artfynd.xlsx
+++ b/artfynd/A 5041-2025 artfynd.xlsx
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Cecilia Persson, Tomas Fasth</t>
+          <t>Tomas Fasth, Cecilia Persson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 5041-2025 artfynd.xlsx
+++ b/artfynd/A 5041-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>126760160</v>
       </c>
       <c r="B3" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>126760187</v>
       </c>
       <c r="B4" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>126760309</v>
       </c>
       <c r="B5" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>126759638</v>
       </c>
       <c r="B6" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Tomas Fasth, Cecilia Persson</t>
+          <t>Cecilia Persson, Tomas Fasth</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 5041-2025 artfynd.xlsx
+++ b/artfynd/A 5041-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1213,6 +1213,117 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128770837</v>
+      </c>
+      <c r="B7" t="n">
+        <v>98591</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Illhargen, Illharjens naturreservat, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>505747</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6363037</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Vetlanda</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Bäckseda</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Räknade minst 10 tuvor på en yta på 1 m2</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Elin Rostedt</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Elin Rostedt, Thomas Rostedt, Agnes Rostedt</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 5041-2025 artfynd.xlsx
+++ b/artfynd/A 5041-2025 artfynd.xlsx
@@ -1218,7 +1218,7 @@
         <v>128770837</v>
       </c>
       <c r="B7" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 5041-2025 artfynd.xlsx
+++ b/artfynd/A 5041-2025 artfynd.xlsx
@@ -1218,7 +1218,7 @@
         <v>128770837</v>
       </c>
       <c r="B7" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 5041-2025 artfynd.xlsx
+++ b/artfynd/A 5041-2025 artfynd.xlsx
@@ -1218,7 +1218,7 @@
         <v>128770837</v>
       </c>
       <c r="B7" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 5041-2025 artfynd.xlsx
+++ b/artfynd/A 5041-2025 artfynd.xlsx
@@ -1218,7 +1218,7 @@
         <v>128770837</v>
       </c>
       <c r="B7" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 5041-2025 artfynd.xlsx
+++ b/artfynd/A 5041-2025 artfynd.xlsx
@@ -1218,7 +1218,7 @@
         <v>128770837</v>
       </c>
       <c r="B7" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 5041-2025 artfynd.xlsx
+++ b/artfynd/A 5041-2025 artfynd.xlsx
@@ -1218,7 +1218,7 @@
         <v>128770837</v>
       </c>
       <c r="B7" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 5041-2025 artfynd.xlsx
+++ b/artfynd/A 5041-2025 artfynd.xlsx
@@ -1218,7 +1218,7 @@
         <v>128770837</v>
       </c>
       <c r="B7" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 5041-2025 artfynd.xlsx
+++ b/artfynd/A 5041-2025 artfynd.xlsx
@@ -1218,7 +1218,7 @@
         <v>128770837</v>
       </c>
       <c r="B7" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 5041-2025 artfynd.xlsx
+++ b/artfynd/A 5041-2025 artfynd.xlsx
@@ -1218,7 +1218,7 @@
         <v>128770837</v>
       </c>
       <c r="B7" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 5041-2025 artfynd.xlsx
+++ b/artfynd/A 5041-2025 artfynd.xlsx
@@ -1218,7 +1218,7 @@
         <v>128770837</v>
       </c>
       <c r="B7" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 5041-2025 artfynd.xlsx
+++ b/artfynd/A 5041-2025 artfynd.xlsx
@@ -1218,7 +1218,7 @@
         <v>128770837</v>
       </c>
       <c r="B7" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 5041-2025 artfynd.xlsx
+++ b/artfynd/A 5041-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>126760160</v>
       </c>
       <c r="B3" t="n">
-        <v>98447</v>
+        <v>98436</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>126760187</v>
       </c>
       <c r="B4" t="n">
-        <v>98447</v>
+        <v>98436</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>126760309</v>
       </c>
       <c r="B5" t="n">
-        <v>98447</v>
+        <v>98436</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>126759638</v>
       </c>
       <c r="B6" t="n">
-        <v>98447</v>
+        <v>98436</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 5041-2025 artfynd.xlsx
+++ b/artfynd/A 5041-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>126760160</v>
       </c>
       <c r="B3" t="n">
-        <v>98436</v>
+        <v>98447</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>126760187</v>
       </c>
       <c r="B4" t="n">
-        <v>98436</v>
+        <v>98447</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>126760309</v>
       </c>
       <c r="B5" t="n">
-        <v>98436</v>
+        <v>98447</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         <v>126759638</v>
       </c>
       <c r="B6" t="n">
-        <v>98436</v>
+        <v>98447</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
